--- a/entrepreneur_forms/034_startup_incubator_cohort_voting_form--entrepreneur_forms.xlsx
+++ b/entrepreneur_forms/034_startup_incubator_cohort_voting_form--entrepreneur_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>incubator_name</t>
+          <t>Incubator Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,30 +548,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mentor_name</t>
+          <t>Mentor Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cohort_id</t>
+          <t>helpfulness_vote</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cohort_id</t>
+          <t>How helpful were the mentors?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vote_type</t>
+          <t>score_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>vote_type</t>
+          <t>Score for mentors' helpfulness</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback_comments</t>
+          <t>score_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feedback_comments</t>
+          <t>Score for review committee's helpfulness</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>score_1</t>
+          <t>score_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>score_1</t>
+          <t>Score for overall incubator experience</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>score_2</t>
+          <t>review_committee_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>score_2</t>
+          <t>Review Committee Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>score_3</t>
+          <t>review_committee_email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>score_3</t>
+          <t>Review Committee Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>score_4</t>
+          <t>review_committee_phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>score_4</t>
+          <t>Review Committee Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>score_5</t>
+          <t>review_committee_helpfulness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>score_5</t>
+          <t>Review committee helpfulness score</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>score_6</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>score_6</t>
+          <t>Overall Experience</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>score_7</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>score_7</t>
+          <t>Additional Feedback</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>score_8</t>
+          <t>committee_helpfulness</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>score_8</t>
+          <t>How helpful was the review committee?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,41 +819,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mentor_comments</t>
+          <t>incubator_id</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mentor_comments</t>
+          <t>Incubator ID</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>review_committee_comments</t>
+          <t>mentor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>review_committee_comments</t>
+          <t>How helpful was the mentor?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>review_committee_name</t>
+          <t>incubator_comments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>review_committee_name</t>
+          <t>Incubator Comments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>review_committee_email</t>
+          <t>committee_name</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>review_committee_email</t>
+          <t>Committee Name</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>review_committee_phone</t>
+          <t>committee_email</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>review_committee_phone</t>
+          <t>Committee Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mentor_name</t>
+          <t>committee_phone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mentor_name</t>
+          <t>Committee Phone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>incubator_name</t>
+          <t>committee</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>incubator_name</t>
+          <t>How helpful was the committee?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,40 +975,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>review_committee</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>review_committee</t>
+          <t>Feedback 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mentor_comments</t>
+          <t>incubator</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mentor_comments</t>
+          <t>Incubator</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,69 +1021,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>incubator_id</t>
+          <t>mentor_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>incubator_id</t>
+          <t>Mentor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>mentor</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>mentor</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1052,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,136 +1080,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vote_type_choices</t>
+          <t>helpfulness_vote_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Very helpful</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vote_type_choices</t>
+          <t>helpfulness_vote_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Somewhat helpful</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vote_type_choices</t>
+          <t>helpfulness_vote_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstain</t>
+          <t>not_very_helpful</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>abstain</t>
+          <t>Not very helpful</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vote_type_choices</t>
+          <t>helpfulness_vote_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>not_at_all_helpful</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>Not at all helpful</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>review_committee_choices</t>
+          <t>committee_helpfulness_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes,_they_were_very_helpful</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes, they were very helpful</t>
+          <t>Very helpful</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>review_committee_choices</t>
+          <t>committee_helpfulness_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no,_they_were_not_very_helpful</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No, they were not very helpful</t>
+          <t>Somewhat helpful</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>review_committee_choices</t>
+          <t>committee_helpfulness_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_sure</t>
+          <t>not_very_helpful</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Not very helpful</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mentor_choices</t>
+          <t>committee_helpfulness_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes,_they_were_very_helpful</t>
+          <t>not_at_all_helpful</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes, they were very helpful</t>
+          <t>Not at all helpful</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no,_they_were_not_very_helpful</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No, they were not very helpful</t>
+          <t>Very helpful</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1238,250 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_sure</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Somewhat helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mentor_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>not_very_helpful</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Not very helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mentor_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>not_at_all_helpful</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not at all helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>committee_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>very_helpful</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Very helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>committee_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>somewhat_helpful</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Somewhat helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>committee_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>not_very_helpful</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not very helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>committee_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>not_at_all_helpful</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not at all helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>incubator_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>very_helpful</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Very helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>incubator_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>somewhat_helpful</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Somewhat helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>incubator_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>not_very_helpful</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not very helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>incubator_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>not_at_all_helpful</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not at all helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mentor_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>very_helpful</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Very helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mentor_2_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>somewhat_helpful</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Somewhat helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mentor_2_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>not_very_helpful</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Not very helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mentor_2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>not_at_all_helpful</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Not at all helpful</t>
         </is>
       </c>
     </row>
